--- a/todolist.xlsx
+++ b/todolist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dateien\Game-projects\scream-gamejam2021\gj_itchio_21\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\gj_itchio_21\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59CF143C-6F9C-45EC-A328-0352EA186F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E07B636-1588-4542-811A-9D50C80644F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
   <si>
     <t>Good To Have</t>
   </si>
@@ -137,12 +137,36 @@
   <si>
     <t>vfx</t>
   </si>
+  <si>
+    <t>Aaron</t>
+  </si>
+  <si>
+    <t>Boris</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>Tobi</t>
+  </si>
+  <si>
+    <t>blender models</t>
+  </si>
+  <si>
+    <t>car conroller</t>
+  </si>
+  <si>
+    <t>Main car</t>
+  </si>
+  <si>
+    <t>text box sprites</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,8 +204,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -212,6 +251,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -225,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -236,6 +281,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -516,13 +564,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="21" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -536,9 +584,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -553,8 +601,20 @@
       <c r="H4" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>2</v>
       </c>
@@ -567,8 +627,20 @@
       <c r="I5" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>24</v>
       </c>
@@ -581,8 +653,12 @@
       <c r="I6" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L6" s="12"/>
+      <c r="N6" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
@@ -595,8 +671,11 @@
       <c r="I7" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N7" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
@@ -610,7 +689,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
@@ -621,7 +700,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
@@ -629,7 +708,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
         <v>13</v>
       </c>
@@ -637,14 +716,14 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F12" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>3</v>
       </c>
@@ -652,18 +731,20 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10"/>
+    </row>
+    <row r="20" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/todolist.xlsx
+++ b/todolist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11010"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dateien\Game-projects\scream-gamejam2021\gj_itchio_21\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaron/Documents/games/scream_jam_game/gj_itchio_21/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59CF143C-6F9C-45EC-A328-0352EA186F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2134F0B-D8A8-BB46-86A8-0340FE364CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Good To Have</t>
   </si>
@@ -33,116 +33,44 @@
     <t>Done</t>
   </si>
   <si>
-    <t>Script</t>
-  </si>
-  <si>
-    <t>Mouse Controller</t>
-  </si>
-  <si>
-    <t>Car Controller</t>
-  </si>
-  <si>
-    <t>Unity</t>
-  </si>
-  <si>
-    <t>Car Models</t>
-  </si>
-  <si>
-    <t>Assets</t>
-  </si>
-  <si>
-    <t>Main Car (interiour)</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Streets</t>
-  </si>
-  <si>
-    <r>
-      <t>scenes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (1("openworld") oder mehr?)</t>
-    </r>
-  </si>
-  <si>
-    <t>Passenger</t>
-  </si>
-  <si>
-    <t>Interactiv (Radio;EngineOnOff</t>
-  </si>
-  <si>
-    <t>soundcontroller</t>
-  </si>
-  <si>
-    <t>music</t>
-  </si>
-  <si>
-    <t>sfx</t>
-  </si>
-  <si>
-    <t>Title Screen</t>
-  </si>
-  <si>
     <t>Work In Progress</t>
   </si>
   <si>
     <t>To Do !</t>
   </si>
   <si>
-    <t>Media and other</t>
-  </si>
-  <si>
-    <t>Blender (low-poly)</t>
-  </si>
-  <si>
-    <t>Universal Character</t>
-  </si>
-  <si>
-    <t>texture tutorial</t>
-  </si>
-  <si>
-    <t>final build</t>
-  </si>
-  <si>
-    <t>AI Cars</t>
-  </si>
-  <si>
-    <t>monsters</t>
-  </si>
-  <si>
-    <t>3d usable sprites</t>
-  </si>
-  <si>
-    <t>monster sprites</t>
-  </si>
-  <si>
-    <t>animations</t>
-  </si>
-  <si>
-    <t>end screen</t>
-  </si>
-  <si>
-    <t>seperate wheels</t>
-  </si>
-  <si>
-    <t>vfx</t>
+    <t>Player Controller</t>
+  </si>
+  <si>
+    <t>Opening Cutscene</t>
+  </si>
+  <si>
+    <t>End Cutscene</t>
+  </si>
+  <si>
+    <t>Map Layout</t>
+  </si>
+  <si>
+    <t>Sfx</t>
+  </si>
+  <si>
+    <t>Musik</t>
+  </si>
+  <si>
+    <t>3d Modelling</t>
+  </si>
+  <si>
+    <t>Briefe</t>
+  </si>
+  <si>
+    <t>Monster Design</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,13 +80,6 @@
     </font>
     <font>
       <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -225,20 +146,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -516,152 +436,93 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="21" width="27.42578125" customWidth="1"/>
+    <col min="1" max="21" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="6"/>
+      <c r="C5" s="7"/>
+    </row>
+    <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F12" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/todolist.xlsx
+++ b/todolist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11010"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\gj_itchio_21\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaron/Documents/games/scream_jam_game/gj_itchio_21/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E07B636-1588-4542-811A-9D50C80644F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97618E2A-DF5B-5741-B4E7-445C41AF31FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3180" yWindow="1320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Good To Have</t>
   </si>
@@ -33,140 +33,44 @@
     <t>Done</t>
   </si>
   <si>
-    <t>Script</t>
-  </si>
-  <si>
-    <t>Mouse Controller</t>
-  </si>
-  <si>
-    <t>Car Controller</t>
-  </si>
-  <si>
-    <t>Unity</t>
-  </si>
-  <si>
-    <t>Car Models</t>
-  </si>
-  <si>
-    <t>Assets</t>
-  </si>
-  <si>
-    <t>Main Car (interiour)</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Streets</t>
-  </si>
-  <si>
-    <r>
-      <t>scenes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (1("openworld") oder mehr?)</t>
-    </r>
-  </si>
-  <si>
-    <t>Passenger</t>
-  </si>
-  <si>
-    <t>Interactiv (Radio;EngineOnOff</t>
-  </si>
-  <si>
-    <t>soundcontroller</t>
-  </si>
-  <si>
-    <t>music</t>
-  </si>
-  <si>
-    <t>sfx</t>
-  </si>
-  <si>
-    <t>Title Screen</t>
-  </si>
-  <si>
     <t>Work In Progress</t>
   </si>
   <si>
     <t>To Do !</t>
   </si>
   <si>
-    <t>Media and other</t>
-  </si>
-  <si>
-    <t>Blender (low-poly)</t>
-  </si>
-  <si>
-    <t>Universal Character</t>
-  </si>
-  <si>
-    <t>texture tutorial</t>
-  </si>
-  <si>
-    <t>final build</t>
-  </si>
-  <si>
-    <t>AI Cars</t>
-  </si>
-  <si>
-    <t>monsters</t>
-  </si>
-  <si>
-    <t>3d usable sprites</t>
-  </si>
-  <si>
-    <t>monster sprites</t>
-  </si>
-  <si>
-    <t>animations</t>
-  </si>
-  <si>
-    <t>end screen</t>
-  </si>
-  <si>
-    <t>seperate wheels</t>
-  </si>
-  <si>
-    <t>vfx</t>
-  </si>
-  <si>
-    <t>Aaron</t>
-  </si>
-  <si>
-    <t>Boris</t>
-  </si>
-  <si>
-    <t>Michael</t>
-  </si>
-  <si>
-    <t>Tobi</t>
-  </si>
-  <si>
-    <t>blender models</t>
-  </si>
-  <si>
-    <t>car conroller</t>
-  </si>
-  <si>
-    <t>Main car</t>
-  </si>
-  <si>
-    <t>text box sprites</t>
+    <t>Player Controller</t>
+  </si>
+  <si>
+    <t>3d Modelling</t>
+  </si>
+  <si>
+    <t>Opening Cutscene</t>
+  </si>
+  <si>
+    <t>Briefe</t>
+  </si>
+  <si>
+    <t>End Cutscene</t>
+  </si>
+  <si>
+    <t>Monster Design</t>
+  </si>
+  <si>
+    <t>Map Layout</t>
+  </si>
+  <si>
+    <t>Sfx</t>
+  </si>
+  <si>
+    <t>Musik</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,13 +80,6 @@
     </font>
     <font>
       <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -220,7 +117,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -251,12 +148,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -270,23 +161,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -565,184 +455,241 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="21" width="27.42578125" customWidth="1"/>
+    <col min="1" max="21" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="5" t="s">
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="8" t="s">
+    </row>
+    <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="4"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+    </row>
+    <row r="5" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="C5" s="6"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+    </row>
+    <row r="6" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+    </row>
+    <row r="7" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L6" s="12"/>
-      <c r="N6" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+    </row>
+    <row r="8" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F12" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
-    </row>
-    <row r="20" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+    </row>
+    <row r="9" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+    </row>
+    <row r="10" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+    </row>
+    <row r="11" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+    </row>
+    <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+    </row>
+    <row r="13" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+    </row>
+    <row r="14" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+    </row>
+    <row r="15" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="11"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+    </row>
+    <row r="16" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="8"/>
+    </row>
+    <row r="20" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/todolist.xlsx
+++ b/todolist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaron/Documents/games/scream_jam_game/gj_itchio_21/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97618E2A-DF5B-5741-B4E7-445C41AF31FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B06667-03B3-0742-8138-3F73411E559E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="1320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
   <si>
     <t>Good To Have</t>
   </si>
@@ -39,31 +39,91 @@
     <t>To Do !</t>
   </si>
   <si>
-    <t>Player Controller</t>
-  </si>
-  <si>
-    <t>3d Modelling</t>
-  </si>
-  <si>
     <t>Opening Cutscene</t>
   </si>
   <si>
-    <t>Briefe</t>
-  </si>
-  <si>
-    <t>End Cutscene</t>
-  </si>
-  <si>
-    <t>Monster Design</t>
-  </si>
-  <si>
-    <t>Map Layout</t>
-  </si>
-  <si>
     <t>Sfx</t>
   </si>
   <si>
     <t>Musik</t>
+  </si>
+  <si>
+    <t>Assets:</t>
+  </si>
+  <si>
+    <t>Türen (2-3 Varianten)</t>
+  </si>
+  <si>
+    <t>Stühle</t>
+  </si>
+  <si>
+    <t>Bürosessel</t>
+  </si>
+  <si>
+    <t>Pflanzen (3-4 Varianten)</t>
+  </si>
+  <si>
+    <t>Tische (3-4 Varianten)</t>
+  </si>
+  <si>
+    <t>Bilderrahmen (2 Varianten)</t>
+  </si>
+  <si>
+    <t>Computer</t>
+  </si>
+  <si>
+    <t>Telephon</t>
+  </si>
+  <si>
+    <t>Ordner (2 Variantern)</t>
+  </si>
+  <si>
+    <t>Geländer von Stiegen</t>
+  </si>
+  <si>
+    <t>Deckenlampen (2 Varianten)</t>
+  </si>
+  <si>
+    <t>Stehlampen (2 Varianten)</t>
+  </si>
+  <si>
+    <t>Mülleimer</t>
+  </si>
+  <si>
+    <t>Schränke (2-3 Varianten)</t>
+  </si>
+  <si>
+    <t>Gemälde (4+ Varianten)</t>
+  </si>
+  <si>
+    <t>Aufzug</t>
+  </si>
+  <si>
+    <t>Teppiche (3-4 Varianten)</t>
+  </si>
+  <si>
+    <t>Tobi</t>
+  </si>
+  <si>
+    <t>Aaron</t>
+  </si>
+  <si>
+    <t>Micheal</t>
+  </si>
+  <si>
+    <t>Anderes:</t>
+  </si>
+  <si>
+    <t>Start Screen</t>
+  </si>
+  <si>
+    <t>Zettel</t>
+  </si>
+  <si>
+    <t>Credits</t>
+  </si>
+  <si>
+    <t>E-Mails</t>
   </si>
 </sst>
 </file>
@@ -73,6 +133,13 @@
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -94,21 +161,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="20"/>
       <color theme="1"/>
@@ -116,8 +168,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri (Body)"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -138,13 +195,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -161,19 +224,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,235 +525,315 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="3"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+    </row>
+    <row r="6" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="D6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+    </row>
+    <row r="7" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="4"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-    </row>
-    <row r="5" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-    </row>
-    <row r="6" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-    </row>
-    <row r="7" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
+      <c r="D7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
     </row>
     <row r="8" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
     </row>
     <row r="9" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
+      <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
     </row>
     <row r="10" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
+      <c r="A10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
     </row>
     <row r="11" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
+      <c r="A11" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
     </row>
     <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
+      <c r="A12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
     </row>
     <row r="13" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
+      <c r="A13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
     </row>
     <row r="14" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
+      <c r="A14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
     </row>
     <row r="15" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="11"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-    </row>
-    <row r="16" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="8"/>
-    </row>
-    <row r="20" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="A15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+    </row>
+    <row r="16" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/todolist.xlsx
+++ b/todolist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaron/Documents/games/scream_jam_game/gj_itchio_21/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B06667-03B3-0742-8138-3F73411E559E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645A4AB6-DC18-1347-BACA-2FC16B38DFE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -63,9 +63,6 @@
     <t>Pflanzen (3-4 Varianten)</t>
   </si>
   <si>
-    <t>Tische (3-4 Varianten)</t>
-  </si>
-  <si>
     <t>Bilderrahmen (2 Varianten)</t>
   </si>
   <si>
@@ -123,7 +120,10 @@
     <t>Credits</t>
   </si>
   <si>
-    <t>E-Mails</t>
+    <t>Tische (2-3 Varianten)</t>
+  </si>
+  <si>
+    <t>E-Mails (3)</t>
   </si>
 </sst>
 </file>
@@ -543,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -551,10 +551,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -562,10 +562,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -604,13 +604,13 @@
         <v>11</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" s="7"/>
       <c r="H6" s="7"/>
@@ -623,14 +623,14 @@
     </row>
     <row r="7" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E7" s="7"/>
       <c r="H7" s="7"/>
@@ -643,10 +643,10 @@
     </row>
     <row r="8" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -663,7 +663,7 @@
     </row>
     <row r="9" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -680,10 +680,10 @@
     </row>
     <row r="10" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -699,10 +699,10 @@
     </row>
     <row r="11" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -718,10 +718,10 @@
     </row>
     <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -738,10 +738,10 @@
     </row>
     <row r="13" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -758,7 +758,7 @@
     </row>
     <row r="14" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -776,7 +776,7 @@
     </row>
     <row r="15" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="7"/>
@@ -794,39 +794,39 @@
     </row>
     <row r="16" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/todolist.xlsx
+++ b/todolist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaron/Documents/games/scream_jam_game/gj_itchio_21/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645A4AB6-DC18-1347-BACA-2FC16B38DFE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2270C64-14F9-CE4E-84CF-97AF772CA417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -174,7 +174,7 @@
       <name val="Calibri (Body)"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -205,12 +205,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -236,8 +230,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -547,7 +541,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="12" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
@@ -564,7 +558,7 @@
       <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>30</v>
       </c>
       <c r="D4" s="4"/>
@@ -600,7 +594,7 @@
       <c r="N5" s="7"/>
     </row>
     <row r="6" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="7" t="s">
@@ -642,7 +636,7 @@
       <c r="N7" s="7"/>
     </row>
     <row r="8" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -737,7 +731,7 @@
       <c r="N12" s="7"/>
     </row>
     <row r="13" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="10" t="s">
         <v>16</v>
       </c>
       <c r="B13" t="s">
@@ -793,7 +787,7 @@
       <c r="N15" s="7"/>
     </row>
     <row r="16" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="10" t="s">
         <v>19</v>
       </c>
       <c r="B16" t="s">
@@ -806,7 +800,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="10" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="7" t="s">

--- a/todolist.xlsx
+++ b/todolist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaron/Documents/games/scream_jam_game/gj_itchio_21/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2270C64-14F9-CE4E-84CF-97AF772CA417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB715DF-08FE-A14C-BD15-EA113BEFD284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
   <si>
     <t>Good To Have</t>
   </si>
@@ -78,9 +78,6 @@
     <t>Geländer von Stiegen</t>
   </si>
   <si>
-    <t>Deckenlampen (2 Varianten)</t>
-  </si>
-  <si>
     <t>Stehlampen (2 Varianten)</t>
   </si>
   <si>
@@ -124,6 +121,9 @@
   </si>
   <si>
     <t>E-Mails (3)</t>
+  </si>
+  <si>
+    <t>Aaron, Tobi</t>
   </si>
 </sst>
 </file>
@@ -174,7 +174,7 @@
       <name val="Calibri (Body)"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -205,6 +205,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -218,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -232,6 +238,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -537,7 +544,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -545,10 +552,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -556,10 +563,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -576,7 +583,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -598,13 +605,13 @@
         <v>11</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6" s="7"/>
       <c r="H6" s="7"/>
@@ -616,15 +623,17 @@
       <c r="N6" s="7"/>
     </row>
     <row r="7" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="1" t="s">
+      <c r="A7" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7" s="7"/>
       <c r="H7" s="7"/>
@@ -640,12 +649,14 @@
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -656,10 +667,12 @@
       <c r="N8" s="7"/>
     </row>
     <row r="9" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="7"/>
+      <c r="A9" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
@@ -677,7 +690,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -696,7 +709,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -715,7 +728,7 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -735,7 +748,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -751,10 +764,10 @@
       <c r="N13" s="7"/>
     </row>
     <row r="14" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="7"/>
+      <c r="B14" s="8"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
@@ -769,10 +782,12 @@
       <c r="N14" s="7"/>
     </row>
     <row r="15" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="8"/>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
@@ -787,42 +802,35 @@
       <c r="N15" s="7"/>
     </row>
     <row r="16" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>23</v>
+      <c r="A19" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" t="s">
-        <v>26</v>
-      </c>
-    </row>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/todolist.xlsx
+++ b/todolist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11010"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaron/Documents/games/scream_jam_game/gj_itchio_21/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dateien\Game-projects\scream-gamejam2021\gj_itchio_21\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB715DF-08FE-A14C-BD15-EA113BEFD284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F202E0-D367-43B4-92C4-F31F2F076C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -130,7 +130,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,14 +234,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -520,16 +520,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="21" width="27.5" customWidth="1"/>
+    <col min="1" max="21" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="30" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -539,7 +539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="30" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
@@ -547,25 +547,25 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:14" ht="30" customHeight="1">
+      <c r="A3" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="13" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:14" ht="30" customHeight="1">
+      <c r="A4" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>29</v>
       </c>
       <c r="D4" s="4"/>
@@ -578,8 +578,8 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:14" ht="30" customHeight="1">
+      <c r="A5" s="9" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
@@ -600,14 +600,14 @@
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
     </row>
-    <row r="6" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:14" ht="30" customHeight="1">
+      <c r="A6" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="12" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="7" t="s">
@@ -622,14 +622,14 @@
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
     </row>
-    <row r="7" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
+    <row r="7" spans="1:14" ht="30" customHeight="1">
+      <c r="A7" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="7" t="s">
@@ -644,8 +644,8 @@
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
     </row>
-    <row r="8" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:14" ht="30" customHeight="1">
+      <c r="A8" s="9" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -666,8 +666,8 @@
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
     </row>
-    <row r="9" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
+    <row r="9" spans="1:14" ht="30" customHeight="1">
+      <c r="A9" s="12" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="7" t="s">
@@ -685,8 +685,8 @@
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
     </row>
-    <row r="10" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="10" t="s">
+    <row r="10" spans="1:14" ht="30" customHeight="1">
+      <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="7" t="s">
@@ -704,8 +704,8 @@
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
     </row>
-    <row r="11" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
+    <row r="11" spans="1:14" ht="30" customHeight="1">
+      <c r="A11" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="7" t="s">
@@ -723,8 +723,8 @@
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
     </row>
-    <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
+    <row r="12" spans="1:14" ht="30" customHeight="1">
+      <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B12" t="s">
@@ -743,8 +743,8 @@
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
     </row>
-    <row r="13" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
+    <row r="13" spans="1:14" ht="30" customHeight="1">
+      <c r="A13" s="9" t="s">
         <v>16</v>
       </c>
       <c r="B13" t="s">
@@ -763,7 +763,7 @@
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
     </row>
-    <row r="14" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="30" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>17</v>
       </c>
@@ -781,8 +781,8 @@
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
     </row>
-    <row r="15" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
+    <row r="15" spans="1:14" ht="30" customHeight="1">
+      <c r="A15" s="9" t="s">
         <v>18</v>
       </c>
       <c r="B15" t="s">
@@ -801,41 +801,41 @@
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
     </row>
-    <row r="16" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="30" customHeight="1">
       <c r="A16" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
+    <row r="17" spans="1:2" ht="30" customHeight="1">
+      <c r="A17" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="13" t="s">
+    <row r="18" spans="1:2" ht="30" customHeight="1">
+      <c r="A18" s="12" t="s">
         <v>22</v>
       </c>
       <c r="B18" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="10" t="s">
+    <row r="19" spans="1:2" ht="30" customHeight="1">
+      <c r="A19" s="9" t="s">
         <v>28</v>
       </c>
       <c r="B19" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:2" ht="30" customHeight="1"/>
+    <row r="21" spans="1:2" ht="30" customHeight="1"/>
+    <row r="22" spans="1:2" ht="30" customHeight="1"/>
+    <row r="23" spans="1:2" ht="30" customHeight="1"/>
+    <row r="24" spans="1:2" ht="30" customHeight="1"/>
+    <row r="25" spans="1:2" ht="30" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/todolist.xlsx
+++ b/todolist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaron/Documents/games/scream_jam_game/gj_itchio_21/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB715DF-08FE-A14C-BD15-EA113BEFD284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1BAA95-2C28-5644-A971-D03F302244E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="57">
   <si>
     <t>Good To Have</t>
   </si>
@@ -124,15 +124,94 @@
   </si>
   <si>
     <t>Aaron, Tobi</t>
+  </si>
+  <si>
+    <t>Section 1 Lichter</t>
+  </si>
+  <si>
+    <t>Section 2 Lichter</t>
+  </si>
+  <si>
+    <t>Assets Section 1</t>
+  </si>
+  <si>
+    <t>Assets Section 2</t>
+  </si>
+  <si>
+    <t>Textur Wand</t>
+  </si>
+  <si>
+    <t>Textur Decke Section 1</t>
+  </si>
+  <si>
+    <t>Textur Decke Section 2</t>
+  </si>
+  <si>
+    <t>E-Mails</t>
+  </si>
+  <si>
+    <t>Music Implimentation</t>
+  </si>
+  <si>
+    <t>Music bei E-mails</t>
+  </si>
+  <si>
+    <t>Cutscene</t>
+  </si>
+  <si>
+    <t>Title Screen</t>
+  </si>
+  <si>
+    <t>Boden Texturen platzieren</t>
+  </si>
+  <si>
+    <t>Hitboxen Assets</t>
+  </si>
+  <si>
+    <t>Enemy Section 2 Waypoints</t>
+  </si>
+  <si>
+    <t>Lift</t>
+  </si>
+  <si>
+    <t>key card</t>
+  </si>
+  <si>
+    <t>Zettel Desgins</t>
+  </si>
+  <si>
+    <t>Passcode</t>
+  </si>
+  <si>
+    <t>Boris</t>
+  </si>
+  <si>
+    <t>Gemälde</t>
+  </si>
+  <si>
+    <t>Boris, Tobi</t>
+  </si>
+  <si>
+    <t>Ambience Sfx</t>
+  </si>
+  <si>
+    <t>Aaron, Boris</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -170,6 +249,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri (Body)"/>
     </font>
@@ -224,21 +308,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -546,6 +633,7 @@
       <c r="C2" s="4" t="s">
         <v>26</v>
       </c>
+      <c r="E2" s="14"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
@@ -557,6 +645,12 @@
       <c r="C3" s="9" t="s">
         <v>27</v>
       </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
@@ -569,8 +663,12 @@
         <v>29</v>
       </c>
       <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="E4" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>52</v>
+      </c>
       <c r="G4" s="4"/>
       <c r="H4" s="3"/>
       <c r="K4" s="6"/>
@@ -589,8 +687,12 @@
         <v>4</v>
       </c>
       <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="E5" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>24</v>
+      </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
@@ -613,7 +715,12 @@
       <c r="D6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>24</v>
+      </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -635,7 +742,12 @@
       <c r="D7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="E7" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>24</v>
+      </c>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -657,7 +769,12 @@
       <c r="D8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>52</v>
+      </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
@@ -675,7 +792,12 @@
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
+      <c r="E9" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>52</v>
+      </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
@@ -694,7 +816,12 @@
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
+      <c r="E10" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>25</v>
+      </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
@@ -713,7 +840,12 @@
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
+      <c r="E11" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
@@ -732,8 +864,12 @@
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="E12" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>23</v>
+      </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -752,8 +888,12 @@
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
+      <c r="E13" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>23</v>
+      </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
@@ -770,8 +910,12 @@
       <c r="B14" s="8"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="E14" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>23</v>
+      </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
@@ -790,8 +934,12 @@
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="E15" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>52</v>
+      </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
@@ -805,37 +953,96 @@
       <c r="A16" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E16" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E17" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="13" t="s">
         <v>22</v>
       </c>
       <c r="B18" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E18" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
         <v>28</v>
       </c>
       <c r="B19" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="E19" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E23" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E24" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/todolist.xlsx
+++ b/todolist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaron/Documents/games/scream_jam_game/gj_itchio_21/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1BAA95-2C28-5644-A971-D03F302244E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB715DF-08FE-A14C-BD15-EA113BEFD284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
   <si>
     <t>Good To Have</t>
   </si>
@@ -124,94 +124,15 @@
   </si>
   <si>
     <t>Aaron, Tobi</t>
-  </si>
-  <si>
-    <t>Section 1 Lichter</t>
-  </si>
-  <si>
-    <t>Section 2 Lichter</t>
-  </si>
-  <si>
-    <t>Assets Section 1</t>
-  </si>
-  <si>
-    <t>Assets Section 2</t>
-  </si>
-  <si>
-    <t>Textur Wand</t>
-  </si>
-  <si>
-    <t>Textur Decke Section 1</t>
-  </si>
-  <si>
-    <t>Textur Decke Section 2</t>
-  </si>
-  <si>
-    <t>E-Mails</t>
-  </si>
-  <si>
-    <t>Music Implimentation</t>
-  </si>
-  <si>
-    <t>Music bei E-mails</t>
-  </si>
-  <si>
-    <t>Cutscene</t>
-  </si>
-  <si>
-    <t>Title Screen</t>
-  </si>
-  <si>
-    <t>Boden Texturen platzieren</t>
-  </si>
-  <si>
-    <t>Hitboxen Assets</t>
-  </si>
-  <si>
-    <t>Enemy Section 2 Waypoints</t>
-  </si>
-  <si>
-    <t>Lift</t>
-  </si>
-  <si>
-    <t>key card</t>
-  </si>
-  <si>
-    <t>Zettel Desgins</t>
-  </si>
-  <si>
-    <t>Passcode</t>
-  </si>
-  <si>
-    <t>Boris</t>
-  </si>
-  <si>
-    <t>Gemälde</t>
-  </si>
-  <si>
-    <t>Boris, Tobi</t>
-  </si>
-  <si>
-    <t>Ambience Sfx</t>
-  </si>
-  <si>
-    <t>Aaron, Boris</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -249,11 +170,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri (Body)"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri (Body)"/>
     </font>
@@ -308,24 +224,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -633,7 +546,6 @@
       <c r="C2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="14"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
@@ -645,12 +557,6 @@
       <c r="C3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" t="s">
-        <v>52</v>
-      </c>
     </row>
     <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
@@ -663,12 +569,8 @@
         <v>29</v>
       </c>
       <c r="D4" s="4"/>
-      <c r="E4" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>52</v>
-      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="3"/>
       <c r="K4" s="6"/>
@@ -687,12 +589,8 @@
         <v>4</v>
       </c>
       <c r="D5" s="7"/>
-      <c r="E5" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>24</v>
-      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
@@ -715,12 +613,7 @@
       <c r="D6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>24</v>
-      </c>
+      <c r="E6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -742,12 +635,7 @@
       <c r="D7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>24</v>
-      </c>
+      <c r="E7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -769,12 +657,7 @@
       <c r="D8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>52</v>
-      </c>
+      <c r="E8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
@@ -792,12 +675,7 @@
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>52</v>
-      </c>
+      <c r="E9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
@@ -816,12 +694,7 @@
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
-      <c r="E10" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>25</v>
-      </c>
+      <c r="E10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
@@ -840,12 +713,7 @@
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
-      <c r="E11" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>54</v>
-      </c>
+      <c r="E11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
@@ -864,12 +732,8 @@
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
-      <c r="E12" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>23</v>
-      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -888,12 +752,8 @@
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
-      <c r="E13" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>23</v>
-      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
@@ -910,12 +770,8 @@
       <c r="B14" s="8"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>23</v>
-      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
@@ -934,12 +790,8 @@
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
-      <c r="E15" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>52</v>
-      </c>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
@@ -953,96 +805,37 @@
       <c r="A16" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="13" t="s">
         <v>22</v>
       </c>
       <c r="B18" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
         <v>28</v>
       </c>
       <c r="B19" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E20" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E21" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E22" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E23" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E24" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    </row>
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
